--- a/data/food_composition_units.xlsx
+++ b/data/food_composition_units.xlsx
@@ -1,26 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/faridannam/Desktop/indonesia_fct/datasets/2_process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF65C44-4F07-4C45-93C1-DC5A922B562E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C1B1A7-0649-F246-98C2-FA1F9A8333AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="200" yWindow="1440" windowWidth="35640" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="38400" yWindow="2000" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="478">
+  <si>
+    <t>coicop_code</t>
+  </si>
+  <si>
+    <t>susenas_code</t>
+  </si>
+  <si>
+    <t>susenas_item</t>
+  </si>
+  <si>
+    <t>unit_id</t>
+  </si>
+  <si>
+    <t>unit_en</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>unit_source</t>
+  </si>
   <si>
     <t>PADI-PADIAN</t>
   </si>
@@ -451,16 +491,16 @@
     <t>Susu cair pabrik</t>
   </si>
   <si>
-    <t>Kotak kecil (±250 ml)</t>
-  </si>
-  <si>
-    <t>Small box (±250 ml)</t>
+    <t>Kotak kecil (±200 ml)</t>
+  </si>
+  <si>
+    <t>Small box (±200 ml)</t>
   </si>
   <si>
     <t>ml</t>
   </si>
   <si>
-    <t>1 small carton = ±250 ml</t>
+    <t>1 small carton = ±200 ml</t>
   </si>
   <si>
     <t>01.1.4.3.005</t>
@@ -469,13 +509,13 @@
     <t>Susu kental manis</t>
   </si>
   <si>
-    <t>Kaleng (±397 gr)</t>
-  </si>
-  <si>
-    <t>Can (±397 g)</t>
-  </si>
-  <si>
-    <t>1 can = ±397 g</t>
+    <t>Kaleng (±370 gr)</t>
+  </si>
+  <si>
+    <t>Can (±370 g)</t>
+  </si>
+  <si>
+    <t>1 can = ±370 g</t>
   </si>
   <si>
     <t>01.1.4.3.001/2</t>
@@ -496,6 +536,12 @@
     <t>Susu lainnya dan hasil lain dari susu</t>
   </si>
   <si>
+    <t>Average from other items in the same category (items 67-70)</t>
+  </si>
+  <si>
+    <t>group mean of the other items in the food group, Farid 2026-09-03</t>
+  </si>
+  <si>
     <t>SAYUR-SAYURAN</t>
   </si>
   <si>
@@ -826,6 +872,9 @@
     <t>Minyak dan kelapa lainnya</t>
   </si>
   <si>
+    <t>Average from other items in the same category (items 121-123)</t>
+  </si>
+  <si>
     <t>BAHAN MINUMAN</t>
   </si>
   <si>
@@ -889,6 +938,9 @@
     <t>Bahan minuman lainnya</t>
   </si>
   <si>
+    <t>Average from other items in the same category (items 126-131), 70.33 rounded to 70 g</t>
+  </si>
+  <si>
     <t>BUMBU-BUMBUAN</t>
   </si>
   <si>
@@ -1021,6 +1073,9 @@
     <t>Lainnya</t>
   </si>
   <si>
+    <t>Average from other items in the same category (items 147-149)</t>
+  </si>
+  <si>
     <t>MAKANAN MINUMAN JADI</t>
   </si>
   <si>
@@ -1276,6 +1331,9 @@
     <t>Makanan jadi lainnya</t>
   </si>
   <si>
+    <t>Average from other items in the same category (items 152-173)</t>
+  </si>
+  <si>
     <t>11.1.1.1.058</t>
   </si>
   <si>
@@ -1409,39 +1467,15 @@
   </si>
   <si>
     <t>Rokok dan tembakau Lainnya</t>
-  </si>
-  <si>
-    <t>coicop_code</t>
-  </si>
-  <si>
-    <t>susenas_code</t>
-  </si>
-  <si>
-    <t>susenas_item</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>unit_source</t>
-  </si>
-  <si>
-    <t>unit</t>
-  </si>
-  <si>
-    <t>unit_en</t>
-  </si>
-  <si>
-    <t>unit_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1473,7 +1507,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1486,7 +1520,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC0CB"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1517,7 +1552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1526,9 +1561,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1543,7 +1575,23 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1886,41 +1934,41 @@
     <col min="3" max="3" width="77.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="102" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="113.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="2"/>
+    <col min="10" max="11" width="10.83203125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>465</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>466</v>
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>469</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>467</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>468</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -1928,181 +1976,181 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
+      <c r="A3" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2">
+        <v>12</v>
+      </c>
+      <c r="F3" s="9">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
+      <c r="A4" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2">
+        <v>12</v>
+      </c>
+      <c r="F4" s="9">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>8</v>
+      <c r="A5" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="2">
+        <v>12</v>
+      </c>
+      <c r="F5" s="9">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
+      <c r="A6" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2">
+        <v>12</v>
+      </c>
+      <c r="F6" s="9">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
+      <c r="A7" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2">
+        <v>12</v>
+      </c>
+      <c r="F7" s="9">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
+      <c r="A8" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2">
+        <v>12</v>
+      </c>
+      <c r="F8" s="9">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -2110,210 +2158,210 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>17</v>
+      <c r="A10" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2">
+        <v>12</v>
+      </c>
+      <c r="F10" s="9">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>19</v>
+      <c r="A11" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2">
+        <v>12</v>
+      </c>
+      <c r="F11" s="9">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>21</v>
+      <c r="A12" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="2">
+        <v>12</v>
+      </c>
+      <c r="F12" s="9">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
+      <c r="A13" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="2">
+        <v>12</v>
+      </c>
+      <c r="F13" s="9">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>25</v>
+      <c r="A14" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="B14" s="1">
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="9">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="B15" s="1">
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="2">
+        <v>12</v>
+      </c>
+      <c r="F15" s="9">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>28</v>
+      <c r="A16" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="B16" s="1">
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="2">
+        <v>12</v>
+      </c>
+      <c r="F16" s="9">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -2321,1022 +2369,1022 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>31</v>
+      <c r="A18" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="B18" s="1">
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="2">
+        <v>12</v>
+      </c>
+      <c r="F18" s="9">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>33</v>
+      <c r="A19" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="B19" s="1">
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="2">
+        <v>12</v>
+      </c>
+      <c r="F19" s="9">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>35</v>
+      <c r="A20" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="B20" s="1">
         <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="2">
+        <v>12</v>
+      </c>
+      <c r="F20" s="9">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>37</v>
+      <c r="A21" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="B21" s="1">
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="2">
+        <v>12</v>
+      </c>
+      <c r="F21" s="9">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>39</v>
+      <c r="A22" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="B22" s="1">
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="2">
+        <v>12</v>
+      </c>
+      <c r="F22" s="9">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>41</v>
+      <c r="A23" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="B23" s="1">
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="2">
+        <v>12</v>
+      </c>
+      <c r="F23" s="9">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>43</v>
+      <c r="A24" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="B24" s="1">
         <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="2">
+        <v>12</v>
+      </c>
+      <c r="F24" s="9">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>45</v>
+      <c r="A25" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="B25" s="1">
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F25" s="2">
+        <v>12</v>
+      </c>
+      <c r="F25" s="9">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>47</v>
+      <c r="A26" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="B26" s="1">
         <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="2">
+        <v>12</v>
+      </c>
+      <c r="F26" s="9">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>49</v>
+      <c r="A27" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="B27" s="1">
         <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="2">
+        <v>12</v>
+      </c>
+      <c r="F27" s="9">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>51</v>
+      <c r="A28" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="B28" s="1">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F28" s="2">
+        <v>12</v>
+      </c>
+      <c r="F28" s="9">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>53</v>
+      <c r="A29" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="B29" s="1">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="2">
+        <v>12</v>
+      </c>
+      <c r="F29" s="9">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>55</v>
+      <c r="A30" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="B30" s="1">
         <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F30" s="2">
+        <v>12</v>
+      </c>
+      <c r="F30" s="9">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>57</v>
+      <c r="A31" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="B31" s="1">
         <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" s="2">
+        <v>12</v>
+      </c>
+      <c r="F31" s="9">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>59</v>
+      <c r="A32" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="B32" s="1">
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="2">
+        <v>12</v>
+      </c>
+      <c r="F32" s="9">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>61</v>
+      <c r="A33" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="B33" s="1">
         <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="2">
+        <v>12</v>
+      </c>
+      <c r="F33" s="9">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>63</v>
+      <c r="A34" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="B34" s="1">
         <v>33</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F34" s="2">
+        <v>12</v>
+      </c>
+      <c r="F34" s="9">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
-        <v>65</v>
+      <c r="A35" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="B35" s="1">
         <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="2">
+        <v>12</v>
+      </c>
+      <c r="F35" s="9">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>67</v>
+      <c r="A36" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="B36" s="1">
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="2">
+        <v>12</v>
+      </c>
+      <c r="F36" s="9">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
-        <v>69</v>
+      <c r="A37" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="B37" s="1">
         <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F37" s="2">
+        <v>12</v>
+      </c>
+      <c r="F37" s="9">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
-        <v>71</v>
+      <c r="A38" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="B38" s="1">
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F38" s="2">
+        <v>12</v>
+      </c>
+      <c r="F38" s="9">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
-        <v>73</v>
+      <c r="A39" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="B39" s="1">
         <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F39" s="2">
+        <v>12</v>
+      </c>
+      <c r="F39" s="9">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>75</v>
+      <c r="A40" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="B40" s="1">
         <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F40" s="2">
+        <v>87</v>
+      </c>
+      <c r="F40" s="9">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>80</v>
+      <c r="A41" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="B41" s="1">
         <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F41" s="2">
+        <v>87</v>
+      </c>
+      <c r="F41" s="9">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>82</v>
+      <c r="A42" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="B42" s="1">
         <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F42" s="2">
+        <v>87</v>
+      </c>
+      <c r="F42" s="9">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>84</v>
+      <c r="A43" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="B43" s="1">
         <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F43" s="2">
+        <v>87</v>
+      </c>
+      <c r="F43" s="9">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
-        <v>86</v>
+      <c r="A44" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="B44" s="1">
         <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F44" s="2">
+      <c r="F44" s="9">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
-        <v>88</v>
+      <c r="A45" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="B45" s="1">
         <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F45" s="2">
+        <v>87</v>
+      </c>
+      <c r="F45" s="9">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
-        <v>90</v>
+      <c r="A46" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="B46" s="1">
         <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F46" s="2">
+        <v>87</v>
+      </c>
+      <c r="F46" s="9">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
-        <v>92</v>
+      <c r="A47" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="B47" s="1">
         <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F47" s="2">
+        <v>87</v>
+      </c>
+      <c r="F47" s="9">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
-        <v>94</v>
+      <c r="A48" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="B48" s="1">
         <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F48" s="2">
+        <v>87</v>
+      </c>
+      <c r="F48" s="9">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>96</v>
+      <c r="A49" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="B49" s="1">
         <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F49" s="2">
+        <v>87</v>
+      </c>
+      <c r="F49" s="9">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>98</v>
+      <c r="A50" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="B50" s="1">
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F50" s="2">
+        <v>87</v>
+      </c>
+      <c r="F50" s="9">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
-        <v>100</v>
+      <c r="A51" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="B51" s="1">
         <v>50</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F51" s="2">
+        <v>87</v>
+      </c>
+      <c r="F51" s="9">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
-        <v>96</v>
+      <c r="A52" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="B52" s="1">
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F52" s="2">
+        <v>87</v>
+      </c>
+      <c r="F52" s="9">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
@@ -3344,268 +3392,268 @@
         <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
-        <v>104</v>
+      <c r="A54" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="B54" s="1">
         <v>53</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" s="2">
+        <v>12</v>
+      </c>
+      <c r="F54" s="9">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
-        <v>106</v>
+      <c r="A55" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="B55" s="1">
         <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F55" s="2">
+        <v>12</v>
+      </c>
+      <c r="F55" s="9">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" s="5" t="s">
-        <v>108</v>
+      <c r="A56" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="B56" s="1">
         <v>55</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F56" s="2">
+        <v>12</v>
+      </c>
+      <c r="F56" s="9">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
-        <v>110</v>
+      <c r="A57" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="B57" s="1">
         <v>56</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="2">
+        <v>12</v>
+      </c>
+      <c r="F57" s="9">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
-        <v>112</v>
+      <c r="A58" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="B58" s="1">
         <v>57</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="2">
+        <v>12</v>
+      </c>
+      <c r="F58" s="9">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
-        <v>114</v>
+      <c r="A59" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="B59" s="1">
         <v>58</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="2">
+        <v>12</v>
+      </c>
+      <c r="F59" s="9">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" s="5" t="s">
-        <v>116</v>
+      <c r="A60" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="B60" s="1">
         <v>59</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="2">
+        <v>12</v>
+      </c>
+      <c r="F60" s="9">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
-        <v>118</v>
+      <c r="A61" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="B61" s="1">
         <v>60</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F61" s="2">
+        <v>12</v>
+      </c>
+      <c r="F61" s="9">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
-        <v>120</v>
+      <c r="A62" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="B62" s="1">
         <v>61</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="2">
+        <v>12</v>
+      </c>
+      <c r="F62" s="9">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
@@ -3613,250 +3661,268 @@
         <v>62</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B64" s="7">
+      <c r="A64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="1">
         <v>63</v>
       </c>
-      <c r="C64" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F64" s="8">
+      <c r="C64" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F64" s="9">
         <v>60</v>
       </c>
-      <c r="G64" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>129</v>
+      <c r="G64" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B65" s="7">
+      <c r="A65" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" s="1">
         <v>64</v>
       </c>
-      <c r="C65" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F65" s="8">
+      <c r="C65" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F65" s="9">
         <v>50</v>
       </c>
-      <c r="G65" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>133</v>
+      <c r="G65" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" s="1">
+        <v>65</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="7">
-        <v>65</v>
-      </c>
-      <c r="C66" s="7" t="s">
+      <c r="E66" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F66" s="8">
+      <c r="F66" s="9">
         <v>70</v>
       </c>
-      <c r="G66" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H66" s="8" t="s">
+      <c r="G66" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I66" s="8" t="s">
-        <v>137</v>
+      <c r="H66" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" s="7">
+      <c r="A67" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B67" s="1">
         <v>66</v>
       </c>
-      <c r="C67" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F67" s="8">
+      <c r="C67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F67" s="9">
         <v>60</v>
       </c>
-      <c r="G67" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="I67" s="8" t="s">
-        <v>137</v>
+      <c r="G67" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B68" s="7">
+      <c r="A68" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="1">
         <v>67</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F68" s="8">
-        <v>250</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>5</v>
+      <c r="C68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F68" s="9">
+        <v>200</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B69" s="7">
+      <c r="A69" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" s="1">
         <v>68</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="F69" s="8">
-        <v>397</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>5</v>
+      <c r="C69" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" s="9">
+        <v>370</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="5" t="s">
-        <v>152</v>
+      <c r="A70" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="B70" s="1">
         <v>69</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F70" s="2">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="F70" s="11">
+        <v>0.4</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="5" t="s">
-        <v>154</v>
+      <c r="A71" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B71" s="1">
         <v>70</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F71" s="2">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="F71" s="11">
+        <v>0.4</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A72" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B72" s="1">
+        <v>165</v>
+      </c>
+      <c r="B72" s="6">
         <v>71</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>157</v>
+      <c r="C72" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F72" s="10">
+        <v>342.5</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
@@ -3864,728 +3930,726 @@
         <v>72</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A74" s="5" t="s">
-        <v>159</v>
+      <c r="A74" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="B74" s="1">
         <v>73</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F74" s="2">
+        <v>12</v>
+      </c>
+      <c r="F74" s="9">
         <v>1</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="5" t="s">
-        <v>161</v>
+      <c r="A75" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="B75" s="1">
         <v>74</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F75" s="2">
+        <v>12</v>
+      </c>
+      <c r="F75" s="9">
         <v>1</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" s="5" t="s">
-        <v>163</v>
+      <c r="A76" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="B76" s="1">
         <v>75</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="2">
+        <v>12</v>
+      </c>
+      <c r="F76" s="9">
         <v>1</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A77" s="5" t="s">
-        <v>165</v>
+      <c r="A77" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="B77" s="1">
         <v>76</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F77" s="2">
+        <v>12</v>
+      </c>
+      <c r="F77" s="9">
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
-        <v>167</v>
+      <c r="A78" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="B78" s="1">
         <v>77</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F78" s="2">
+        <v>12</v>
+      </c>
+      <c r="F78" s="9">
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A79" s="5" t="s">
-        <v>169</v>
+      <c r="A79" s="4" t="s">
+        <v>180</v>
       </c>
       <c r="B79" s="1">
         <v>78</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F79" s="2">
+        <v>12</v>
+      </c>
+      <c r="F79" s="9">
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" s="5" t="s">
-        <v>171</v>
+      <c r="A80" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="B80" s="1">
         <v>79</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F80" s="2">
+        <v>12</v>
+      </c>
+      <c r="F80" s="9">
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A81" s="5" t="s">
-        <v>173</v>
+      <c r="A81" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="B81" s="1">
         <v>80</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F81" s="2">
+        <v>12</v>
+      </c>
+      <c r="F81" s="9">
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A82" s="5" t="s">
-        <v>175</v>
+      <c r="A82" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="B82" s="1">
         <v>81</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F82" s="2">
+        <v>12</v>
+      </c>
+      <c r="F82" s="9">
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
-        <v>177</v>
+      <c r="A83" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="B83" s="1">
         <v>82</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="2">
+        <v>12</v>
+      </c>
+      <c r="F83" s="9">
         <v>1</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A84" s="5" t="s">
-        <v>179</v>
+      <c r="A84" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="B84" s="1">
         <v>83</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F84" s="2">
+        <v>12</v>
+      </c>
+      <c r="F84" s="9">
         <v>1</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A85" s="5" t="s">
-        <v>181</v>
+      <c r="A85" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="B85" s="1">
         <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F85" s="2">
+        <v>12</v>
+      </c>
+      <c r="F85" s="9">
         <v>1</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A86" s="5" t="s">
-        <v>183</v>
+      <c r="A86" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="B86" s="1">
         <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F86" s="2">
+        <v>12</v>
+      </c>
+      <c r="F86" s="9">
         <v>1</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A87" s="5" t="s">
-        <v>185</v>
+      <c r="A87" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="B87" s="1">
         <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F87" s="2">
+        <v>12</v>
+      </c>
+      <c r="F87" s="9">
         <v>1</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A88" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B88" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B88" s="1">
         <v>87</v>
       </c>
-      <c r="C88" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="F88" s="8">
+      <c r="C88" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F88" s="9">
         <v>250</v>
       </c>
-      <c r="G88" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="I88" s="9"/>
-    </row>
-    <row r="89" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A89" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B89" s="7">
+      <c r="G88" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B89" s="1">
         <v>88</v>
       </c>
-      <c r="C89" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="F89" s="8">
+      <c r="C89" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G89" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="I89" s="9"/>
+      <c r="E89" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F89" s="9">
+        <v>200</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A90" s="5" t="s">
-        <v>195</v>
+      <c r="A90" s="4" t="s">
+        <v>206</v>
       </c>
       <c r="B90" s="1">
         <v>89</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F90" s="2">
+        <v>12</v>
+      </c>
+      <c r="F90" s="9">
         <v>1</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
-        <v>197</v>
+      <c r="A91" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="B91" s="1">
         <v>90</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="2">
+        <v>12</v>
+      </c>
+      <c r="F91" s="9">
         <v>1</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
-        <v>199</v>
+      <c r="A92" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="B92" s="1">
         <v>91</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F92" s="2">
+        <v>12</v>
+      </c>
+      <c r="F92" s="9">
         <v>1</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A93" s="5" t="s">
-        <v>201</v>
+      <c r="A93" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="B93" s="1">
         <v>92</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F93" s="2">
+        <v>87</v>
+      </c>
+      <c r="F93" s="9">
         <v>1</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A94" s="5" t="s">
-        <v>204</v>
+      <c r="A94" s="4" t="s">
+        <v>215</v>
       </c>
       <c r="B94" s="1">
         <v>93</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F94" s="2">
+        <v>87</v>
+      </c>
+      <c r="F94" s="9">
         <v>1</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A95" s="5" t="s">
-        <v>206</v>
+      <c r="A95" s="4" t="s">
+        <v>217</v>
       </c>
       <c r="B95" s="1">
         <v>94</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F95" s="2">
+        <v>12</v>
+      </c>
+      <c r="F95" s="9">
         <v>1</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A96" s="5" t="s">
-        <v>208</v>
+      <c r="A96" s="4" t="s">
+        <v>219</v>
       </c>
       <c r="B96" s="1">
         <v>95</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F96" s="2">
+        <v>12</v>
+      </c>
+      <c r="F96" s="9">
         <v>1</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A97" s="5" t="s">
-        <v>210</v>
+      <c r="A97" s="4" t="s">
+        <v>221</v>
       </c>
       <c r="B97" s="1">
         <v>96</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F97" s="2">
+        <v>12</v>
+      </c>
+      <c r="F97" s="9">
         <v>1</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A98" s="5" t="s">
-        <v>212</v>
+      <c r="A98" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="B98" s="1">
         <v>97</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F98" s="2">
+        <v>12</v>
+      </c>
+      <c r="F98" s="9">
         <v>1</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
@@ -4593,210 +4657,210 @@
         <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A100" s="5" t="s">
-        <v>215</v>
+      <c r="A100" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="B100" s="1">
         <v>99</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="2">
+        <v>12</v>
+      </c>
+      <c r="F100" s="9">
         <v>1</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A101" s="5" t="s">
-        <v>217</v>
+      <c r="A101" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="B101" s="1">
         <v>100</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="2">
+        <v>12</v>
+      </c>
+      <c r="F101" s="9">
         <v>1</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A102" s="5" t="s">
-        <v>219</v>
+      <c r="A102" s="4" t="s">
+        <v>230</v>
       </c>
       <c r="B102" s="1">
         <v>101</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="2">
+        <v>12</v>
+      </c>
+      <c r="F102" s="9">
         <v>1</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A103" s="5" t="s">
-        <v>221</v>
+      <c r="A103" s="4" t="s">
+        <v>232</v>
       </c>
       <c r="B103" s="1">
         <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F103" s="2">
+        <v>12</v>
+      </c>
+      <c r="F103" s="9">
         <v>1</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A104" s="5" t="s">
-        <v>223</v>
+      <c r="A104" s="4" t="s">
+        <v>234</v>
       </c>
       <c r="B104" s="1">
         <v>103</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F104" s="2">
+        <v>12</v>
+      </c>
+      <c r="F104" s="9">
         <v>1</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A105" s="5" t="s">
-        <v>225</v>
+      <c r="A105" s="4" t="s">
+        <v>236</v>
       </c>
       <c r="B105" s="1">
         <v>104</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F105" s="2">
+        <v>87</v>
+      </c>
+      <c r="F105" s="9">
         <v>1</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A106" s="5" t="s">
-        <v>227</v>
+      <c r="A106" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="B106" s="1">
         <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F106" s="2">
+        <v>87</v>
+      </c>
+      <c r="F106" s="9">
         <v>1</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
@@ -4804,355 +4868,355 @@
         <v>106</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A108" s="5" t="s">
-        <v>230</v>
+      <c r="A108" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="B108" s="1">
         <v>107</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F108" s="2">
+        <v>12</v>
+      </c>
+      <c r="F108" s="9">
         <v>1</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A109" s="5" t="s">
-        <v>232</v>
+      <c r="A109" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="B109" s="1">
         <v>108</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F109" s="2">
+        <v>12</v>
+      </c>
+      <c r="F109" s="9">
         <v>1</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A110" s="5" t="s">
-        <v>234</v>
+      <c r="A110" s="4" t="s">
+        <v>245</v>
       </c>
       <c r="B110" s="1">
         <v>109</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F110" s="2">
+        <v>12</v>
+      </c>
+      <c r="F110" s="9">
         <v>1</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A111" s="5" t="s">
-        <v>236</v>
+      <c r="A111" s="4" t="s">
+        <v>247</v>
       </c>
       <c r="B111" s="1">
         <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F111" s="2">
+        <v>12</v>
+      </c>
+      <c r="F111" s="9">
         <v>1</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A112" s="5" t="s">
-        <v>238</v>
+      <c r="A112" s="4" t="s">
+        <v>249</v>
       </c>
       <c r="B112" s="1">
         <v>111</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F112" s="2">
+        <v>12</v>
+      </c>
+      <c r="F112" s="9">
         <v>1</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A113" s="5" t="s">
-        <v>240</v>
+      <c r="A113" s="4" t="s">
+        <v>251</v>
       </c>
       <c r="B113" s="1">
         <v>112</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F113" s="2">
+        <v>12</v>
+      </c>
+      <c r="F113" s="9">
         <v>1</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A114" s="5" t="s">
-        <v>242</v>
+      <c r="A114" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="B114" s="1">
         <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F114" s="2">
+        <v>12</v>
+      </c>
+      <c r="F114" s="9">
         <v>1</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A115" s="5" t="s">
-        <v>244</v>
+      <c r="A115" s="4" t="s">
+        <v>255</v>
       </c>
       <c r="B115" s="1">
         <v>114</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F115" s="2">
+        <v>12</v>
+      </c>
+      <c r="F115" s="9">
         <v>1</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A116" s="5" t="s">
-        <v>246</v>
+      <c r="A116" s="4" t="s">
+        <v>257</v>
       </c>
       <c r="B116" s="1">
         <v>115</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F116" s="2">
+        <v>12</v>
+      </c>
+      <c r="F116" s="9">
         <v>1</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A117" s="5" t="s">
-        <v>248</v>
+      <c r="A117" s="4" t="s">
+        <v>259</v>
       </c>
       <c r="B117" s="1">
         <v>116</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F117" s="2">
+        <v>12</v>
+      </c>
+      <c r="F117" s="9">
         <v>1</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A118" s="5" t="s">
-        <v>250</v>
+      <c r="A118" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="B118" s="1">
         <v>117</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F118" s="2">
+        <v>12</v>
+      </c>
+      <c r="F118" s="9">
         <v>1</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A119" s="5" t="s">
-        <v>252</v>
+      <c r="A119" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="B119" s="1">
         <v>118</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F119" s="2">
+        <v>12</v>
+      </c>
+      <c r="F119" s="9">
         <v>1</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
@@ -5160,25 +5224,25 @@
         <v>119</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F120" s="2">
+        <v>12</v>
+      </c>
+      <c r="F120" s="9">
         <v>1</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
@@ -5186,103 +5250,120 @@
         <v>120</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A122" s="5" t="s">
-        <v>256</v>
+      <c r="A122" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="B122" s="1">
         <v>121</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F122" s="2">
+        <v>269</v>
+      </c>
+      <c r="F122" s="9">
         <v>1</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A123" s="5" t="s">
-        <v>261</v>
+      <c r="A123" s="4" t="s">
+        <v>272</v>
       </c>
       <c r="B123" s="1">
         <v>122</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F123" s="2">
+        <v>269</v>
+      </c>
+      <c r="F123" s="9">
         <v>1</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A124" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="B124" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B124" s="1">
         <v>123</v>
       </c>
-      <c r="C124" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F124" s="8">
+      <c r="C124" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F124" s="9">
         <v>400</v>
       </c>
-      <c r="G124" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H124" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="I124" s="9"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G124" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B125" s="1">
+        <v>277</v>
+      </c>
+      <c r="B125" s="6">
         <v>124</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>267</v>
+      <c r="C125" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F125" s="10">
+        <v>800</v>
+      </c>
+      <c r="G125" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="I125" s="14" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
@@ -5290,192 +5371,210 @@
         <v>125</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A127" s="5" t="s">
-        <v>269</v>
+      <c r="A127" s="4" t="s">
+        <v>281</v>
       </c>
       <c r="B127" s="1">
         <v>126</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F127" s="2">
+        <v>87</v>
+      </c>
+      <c r="F127" s="9">
         <v>1</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A128" s="5" t="s">
-        <v>271</v>
+      <c r="A128" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="B128" s="1">
         <v>127</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F128" s="2">
+        <v>87</v>
+      </c>
+      <c r="F128" s="9">
         <v>1</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A129" s="5" t="s">
-        <v>273</v>
+      <c r="A129" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="B129" s="1">
         <v>128</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F129" s="2">
+        <v>87</v>
+      </c>
+      <c r="F129" s="9">
         <v>1</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A130" s="5" t="s">
-        <v>275</v>
+      <c r="A130" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="B130" s="1">
         <v>129</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F130" s="2">
+        <v>290</v>
+      </c>
+      <c r="F130" s="9">
         <v>2</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A131" s="5" t="s">
-        <v>280</v>
+      <c r="A131" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="B131" s="1">
         <v>130</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F131" s="2">
+        <v>87</v>
+      </c>
+      <c r="F131" s="9">
         <v>1</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A132" s="5" t="s">
-        <v>282</v>
+      <c r="A132" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="B132" s="1">
         <v>131</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F132" s="2">
+        <v>297</v>
+      </c>
+      <c r="F132" s="9">
         <v>20</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A133" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B133" s="1">
+        <v>299</v>
+      </c>
+      <c r="B133" s="6">
         <v>132</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>288</v>
+      <c r="C133" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D133" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E133" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F133" s="10">
+        <v>70</v>
+      </c>
+      <c r="G133" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="I133" s="14" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
@@ -5483,355 +5582,355 @@
         <v>133</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A135" s="5" t="s">
-        <v>290</v>
+      <c r="A135" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="B135" s="1">
         <v>134</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F135" s="2">
+        <v>305</v>
+      </c>
+      <c r="F135" s="9">
         <v>1</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A136" s="5" t="s">
-        <v>294</v>
+      <c r="A136" s="4" t="s">
+        <v>307</v>
       </c>
       <c r="B136" s="1">
         <v>135</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F136" s="2">
+        <v>305</v>
+      </c>
+      <c r="F136" s="9">
         <v>1</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A137" s="5" t="s">
-        <v>296</v>
+      <c r="A137" s="4" t="s">
+        <v>309</v>
       </c>
       <c r="B137" s="1">
         <v>136</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F137" s="2">
+        <v>305</v>
+      </c>
+      <c r="F137" s="9">
         <v>1</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A138" s="5" t="s">
-        <v>298</v>
+      <c r="A138" s="4" t="s">
+        <v>311</v>
       </c>
       <c r="B138" s="1">
         <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F138" s="2">
+        <v>305</v>
+      </c>
+      <c r="F138" s="9">
         <v>1</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A139" s="5" t="s">
-        <v>300</v>
+      <c r="A139" s="4" t="s">
+        <v>313</v>
       </c>
       <c r="B139" s="1">
         <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F139" s="2">
+        <v>305</v>
+      </c>
+      <c r="F139" s="9">
         <v>1</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A140" s="5" t="s">
-        <v>302</v>
+      <c r="A140" s="4" t="s">
+        <v>315</v>
       </c>
       <c r="B140" s="1">
         <v>139</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F140" s="2">
+        <v>305</v>
+      </c>
+      <c r="F140" s="9">
         <v>1</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A141" s="5" t="s">
-        <v>304</v>
+      <c r="A141" s="4" t="s">
+        <v>317</v>
       </c>
       <c r="B141" s="1">
         <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F141" s="2">
+        <v>319</v>
+      </c>
+      <c r="F141" s="9">
         <v>100</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A142" s="5" t="s">
-        <v>308</v>
+      <c r="A142" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="B142" s="1">
         <v>141</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F142" s="2">
+        <v>305</v>
+      </c>
+      <c r="F142" s="9">
         <v>1</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A143" s="5" t="s">
-        <v>310</v>
+      <c r="A143" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="B143" s="1">
         <v>142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F143" s="2">
+        <v>319</v>
+      </c>
+      <c r="F143" s="9">
         <v>100</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A144" s="5" t="s">
-        <v>312</v>
+      <c r="A144" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="B144" s="1">
         <v>143</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F144" s="2">
+        <v>319</v>
+      </c>
+      <c r="F144" s="9">
         <v>100</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A145" s="5" t="s">
-        <v>314</v>
+      <c r="A145" s="4" t="s">
+        <v>327</v>
       </c>
       <c r="B145" s="1">
         <v>144</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F145" s="2">
+        <v>305</v>
+      </c>
+      <c r="F145" s="9">
         <v>1</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A146" s="5" t="s">
-        <v>316</v>
+      <c r="A146" s="4" t="s">
+        <v>329</v>
       </c>
       <c r="B146" s="1">
         <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F146" s="2">
+        <v>305</v>
+      </c>
+      <c r="F146" s="9">
         <v>1</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
@@ -5839,105 +5938,123 @@
         <v>146</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A148" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="B148" s="7">
+      <c r="A148" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B148" s="1">
         <v>147</v>
       </c>
-      <c r="C148" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="F148" s="8">
+      <c r="C148" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F148" s="9">
         <v>80</v>
       </c>
-      <c r="G148" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H148" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="I148" s="8" t="s">
-        <v>5</v>
+      <c r="G148" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A149" s="5" t="s">
-        <v>324</v>
+      <c r="A149" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="B149" s="1">
         <v>148</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F149" s="2">
+        <v>87</v>
+      </c>
+      <c r="F149" s="9">
         <v>1</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A150" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B150" s="7">
+      <c r="A150" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B150" s="1">
         <v>149</v>
       </c>
-      <c r="C150" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="F150" s="8">
+      <c r="C150" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F150" s="9">
         <v>150</v>
       </c>
-      <c r="G150" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H150" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="I150" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G150" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A151" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="B151" s="1">
+        <v>344</v>
+      </c>
+      <c r="B151" s="6">
         <v>150</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>332</v>
+      <c r="C151" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="D151" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E151" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F151" s="10">
+        <v>110</v>
+      </c>
+      <c r="G151" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="I151" s="14" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
@@ -5945,867 +6062,876 @@
         <v>151</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A153" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="B153" s="7">
+      <c r="A153" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B153" s="1">
         <v>152</v>
       </c>
-      <c r="C153" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="D153" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E153" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="F153" s="8">
+      <c r="C153" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F153" s="9">
         <v>60</v>
       </c>
-      <c r="G153" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H153" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="I153" s="8" t="s">
-        <v>339</v>
+      <c r="G153" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A154" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="B154" s="8">
+      <c r="A154" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B154" s="2">
         <v>153</v>
       </c>
-      <c r="C154" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="F154" s="8">
+      <c r="C154" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F154" s="9">
         <v>80</v>
       </c>
-      <c r="G154" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H154" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="I154" s="8" t="s">
-        <v>343</v>
+      <c r="G154" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A155" s="5" t="s">
-        <v>344</v>
+      <c r="A155" s="4" t="s">
+        <v>358</v>
       </c>
       <c r="B155" s="1">
         <v>154</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F155" s="2">
+        <v>87</v>
+      </c>
+      <c r="F155" s="9">
         <v>1</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A156" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="B156" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B156" s="1">
         <v>155</v>
       </c>
-      <c r="C156" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D156" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="E156" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F156" s="8">
+      <c r="C156" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F156" s="9">
         <v>50</v>
       </c>
-      <c r="G156" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H156" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="I156" s="9"/>
+      <c r="G156" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B157" s="1">
+        <v>156</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D157" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B157" s="7">
-        <v>156</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E157" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F157" s="8">
+      <c r="E157" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F157" s="9">
         <v>50</v>
       </c>
-      <c r="G157" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H157" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="I157" s="8" t="s">
-        <v>353</v>
+      <c r="G157" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A158" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="B158" s="8">
+      <c r="A158" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B158" s="2">
         <v>157</v>
       </c>
-      <c r="C158" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="D158" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E158" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F158" s="8">
+      <c r="C158" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F158" s="9">
         <v>50</v>
       </c>
-      <c r="G158" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H158" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="I158" s="8" t="s">
-        <v>359</v>
+      <c r="G158" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A159" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="B159" s="7">
+      <c r="A159" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B159" s="1">
         <v>158</v>
       </c>
-      <c r="C159" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="D159" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F159" s="8">
+      <c r="C159" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F159" s="9">
         <v>400</v>
       </c>
-      <c r="G159" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H159" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="I159" s="8" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A160" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="B160" s="7">
+      <c r="G159" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B160" s="1">
         <v>159</v>
       </c>
-      <c r="C160" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="D160" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F160" s="8">
+      <c r="C160" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F160" s="9">
         <v>300</v>
       </c>
-      <c r="G160" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H160" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="I160" s="9"/>
+      <c r="G160" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A161" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="B161" s="7">
+      <c r="A161" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B161" s="1">
         <v>160</v>
       </c>
-      <c r="C161" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D161" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F161" s="8">
+      <c r="C161" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F161" s="9">
         <v>250</v>
       </c>
-      <c r="G161" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H161" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="I161" s="8" t="s">
+      <c r="G161" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A162" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B162" s="1">
+        <v>161</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D162" s="2" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A162" s="6" t="s">
+      <c r="E162" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B162" s="7">
-        <v>161</v>
-      </c>
-      <c r="C162" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="D162" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E162" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F162" s="8">
+      <c r="F162" s="9">
         <v>100</v>
       </c>
-      <c r="G162" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H162" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="I162" s="8" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A163" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="B163" s="7">
+      <c r="G162" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B163" s="1">
         <v>162</v>
       </c>
-      <c r="C163" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="D163" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E163" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F163" s="8">
+      <c r="C163" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F163" s="9">
         <v>300</v>
       </c>
-      <c r="G163" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H163" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="I163" s="9"/>
+      <c r="G163" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A164" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="B164" s="7">
+      <c r="A164" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B164" s="1">
         <v>163</v>
       </c>
-      <c r="C164" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D164" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E164" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F164" s="8">
+      <c r="C164" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F164" s="9">
         <v>350</v>
       </c>
-      <c r="G164" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H164" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="I164" s="8" t="s">
-        <v>381</v>
+      <c r="G164" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A165" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="B165" s="7">
+      <c r="A165" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B165" s="1">
         <v>164</v>
       </c>
-      <c r="C165" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D165" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E165" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F165" s="8">
+      <c r="C165" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F165" s="9">
         <v>100</v>
       </c>
-      <c r="G165" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H165" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="I165" s="8" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A166" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="B166" s="7">
+      <c r="G165" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B166" s="1">
         <v>165</v>
       </c>
-      <c r="C166" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D166" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="E166" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="F166" s="8">
+      <c r="C166" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F166" s="9">
         <v>70</v>
       </c>
-      <c r="G166" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H166" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="I166" s="9"/>
+      <c r="G166" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A167" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="B167" s="7">
+      <c r="A167" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B167" s="1">
         <v>166</v>
       </c>
-      <c r="C167" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="D167" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F167" s="8">
+      <c r="C167" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F167" s="9">
         <v>240</v>
       </c>
-      <c r="G167" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H167" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="I167" s="8" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A168" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="B168" s="7">
+      <c r="G167" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B168" s="1">
         <v>167</v>
       </c>
-      <c r="C168" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="D168" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E168" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F168" s="8">
+      <c r="C168" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F168" s="9">
         <v>200</v>
       </c>
-      <c r="G168" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H168" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="I168" s="9"/>
+      <c r="G168" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A169" s="5" t="s">
-        <v>397</v>
+      <c r="A169" s="4" t="s">
+        <v>411</v>
       </c>
       <c r="B169" s="1">
         <v>168</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F169" s="2">
+        <v>87</v>
+      </c>
+      <c r="F169" s="9">
         <v>1</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A170" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="B170" s="7">
+      <c r="A170" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B170" s="1">
         <v>169</v>
       </c>
-      <c r="C170" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="D170" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E170" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F170" s="8">
+      <c r="C170" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F170" s="9">
         <v>40</v>
       </c>
-      <c r="G170" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H170" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="I170" s="8" t="s">
-        <v>374</v>
+      <c r="G170" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A171" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="B171" s="7">
+      <c r="A171" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B171" s="1">
         <v>170</v>
       </c>
-      <c r="C171" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="D171" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F171" s="8">
+      <c r="C171" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F171" s="9">
         <v>40</v>
       </c>
-      <c r="G171" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H171" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="I171" s="8" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A172" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="B172" s="7">
+      <c r="G171" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B172" s="1">
         <v>171</v>
       </c>
-      <c r="C172" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D172" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E172" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F172" s="8">
+      <c r="C172" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F172" s="9">
         <v>30</v>
       </c>
-      <c r="G172" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H172" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="I172" s="9"/>
+      <c r="G172" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A173" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="B173" s="7">
+      <c r="A173" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B173" s="1">
         <v>172</v>
       </c>
-      <c r="C173" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="D173" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E173" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F173" s="8">
+      <c r="C173" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F173" s="9">
         <v>240</v>
       </c>
-      <c r="G173" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H173" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="I173" s="8" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A174" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="B174" s="7">
+      <c r="G173" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B174" s="1">
         <v>173</v>
       </c>
-      <c r="C174" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D174" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="E174" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="F174" s="8">
+      <c r="C174" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F174" s="9">
         <v>150</v>
       </c>
-      <c r="G174" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H174" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="I174" s="9"/>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B175" s="1">
+      <c r="G174" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B175" s="6">
         <v>174</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>417</v>
+      <c r="C175" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E175" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F175" s="10">
+        <v>150</v>
+      </c>
+      <c r="G175" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="I175" s="14" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A176" s="5" t="s">
-        <v>418</v>
+      <c r="A176" s="4" t="s">
+        <v>433</v>
       </c>
       <c r="B176" s="1">
         <v>175</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F176" s="2">
+        <v>269</v>
+      </c>
+      <c r="F176" s="9">
         <v>1</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A177" s="5" t="s">
-        <v>420</v>
+      <c r="A177" s="4" t="s">
+        <v>435</v>
       </c>
       <c r="B177" s="1">
         <v>176</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="F177" s="2">
+        <v>438</v>
+      </c>
+      <c r="F177" s="9">
         <v>1</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="I177" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A178" s="5" t="s">
-        <v>426</v>
+      <c r="A178" s="4" t="s">
+        <v>441</v>
       </c>
       <c r="B178" s="1">
         <v>177</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F178" s="2">
+        <v>443</v>
+      </c>
+      <c r="F178" s="9">
         <v>250</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="I178" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A179" s="5" t="s">
-        <v>430</v>
+      <c r="A179" s="4" t="s">
+        <v>445</v>
       </c>
       <c r="B179" s="1">
         <v>178</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F179" s="2">
+        <v>447</v>
+      </c>
+      <c r="F179" s="9">
         <v>200</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A180" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="B180" s="7">
+      <c r="A180" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B180" s="1">
         <v>179</v>
       </c>
-      <c r="C180" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="E180" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="F180" s="8">
+      <c r="C180" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F180" s="9">
         <v>240</v>
       </c>
-      <c r="G180" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="H180" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="I180" s="8" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A181" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="B181" s="7">
+      <c r="G180" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B181" s="1">
         <v>180</v>
       </c>
-      <c r="C181" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="D181" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="E181" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="F181" s="8">
+      <c r="C181" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F181" s="9">
         <v>60</v>
       </c>
-      <c r="G181" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H181" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="I181" s="9"/>
-    </row>
-    <row r="182" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A182" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="B182" s="7">
+      <c r="G181" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B182" s="1">
         <v>181</v>
       </c>
-      <c r="C182" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E182" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F182" s="8">
+      <c r="C182" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F182" s="9">
         <v>200</v>
       </c>
-      <c r="G182" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H182" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="I182" s="9"/>
+      <c r="G182" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A183" s="5" t="s">
-        <v>447</v>
+      <c r="A183" s="4" t="s">
+        <v>462</v>
       </c>
       <c r="B183" s="1">
         <v>182</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F183" s="2">
+        <v>269</v>
+      </c>
+      <c r="F183" s="9">
         <v>1</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I183" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
@@ -6813,123 +6939,123 @@
         <v>183</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A185" s="5" t="s">
-        <v>450</v>
+      <c r="A185" s="4" t="s">
+        <v>465</v>
       </c>
       <c r="B185" s="1">
         <v>184</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F185" s="2">
+        <v>468</v>
+      </c>
+      <c r="F185" s="9">
         <v>1</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A186" s="5" t="s">
-        <v>456</v>
+      <c r="A186" s="4" t="s">
+        <v>471</v>
       </c>
       <c r="B186" s="1">
         <v>185</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F186" s="2">
+        <v>468</v>
+      </c>
+      <c r="F186" s="9">
         <v>1</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A187" s="5" t="s">
-        <v>458</v>
+      <c r="A187" s="4" t="s">
+        <v>473</v>
       </c>
       <c r="B187" s="1">
         <v>186</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F187" s="2">
+        <v>468</v>
+      </c>
+      <c r="F187" s="9">
         <v>1</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A188" s="5" t="s">
-        <v>460</v>
+      <c r="A188" s="4" t="s">
+        <v>475</v>
       </c>
       <c r="B188" s="1">
         <v>187</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F188" s="2">
+        <v>87</v>
+      </c>
+      <c r="F188" s="9">
         <v>1</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
@@ -6937,7 +7063,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/data/food_composition_units.xlsx
+++ b/data/food_composition_units.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/faridannam/Desktop/indonesia_fct/datasets/2_process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C1B1A7-0649-F246-98C2-FA1F9A8333AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6768C00C-F91B-7649-B00D-F7EEED2348F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="38400" yWindow="2000" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="2000" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="480">
   <si>
     <t>coicop_code</t>
   </si>
@@ -536,6 +523,9 @@
     <t>Susu lainnya dan hasil lain dari susu</t>
   </si>
   <si>
+    <t>Gram</t>
+  </si>
+  <si>
     <t>Average from other items in the same category (items 67-70)</t>
   </si>
   <si>
@@ -845,501 +835,501 @@
     <t>Liter</t>
   </si>
   <si>
+    <t>1 liter = 920 g at a density of 0.92 g/ml. Sources: FAO/INFOODS Density Database version 2.0 (2012), coconut oil 0.924 g/ml; USDA SR Legacy 171412 Oil, coconut, 1 cup = 218 g (0.92 g/ml)</t>
+  </si>
+  <si>
+    <t>01.1.5.4.001/4</t>
+  </si>
+  <si>
+    <t>Minyak goreng (kelapa sawit, bunga matahari)</t>
+  </si>
+  <si>
+    <t>1 liter = 920 g at a density of 0.92 g/ml. Sources: FAO/INFOODS Density Database version 2.0 (2012), palm oil 0.915 to 0.924 g/ml; USDA SR Legacy 171015 Oil, palm, 1 cup = 216 g (0.91 g/ml)</t>
+  </si>
+  <si>
+    <t>01.1.6.7.033</t>
+  </si>
+  <si>
+    <t>Kelapa (tidak termasuk santan instan)</t>
+  </si>
+  <si>
+    <t>01.1.5.1/52/53/54</t>
+  </si>
+  <si>
+    <t>Minyak dan kelapa lainnya</t>
+  </si>
+  <si>
+    <t>Average from other items in the same category (items 121-123): (920 + 920 + 400) / 3 = 746.67 g</t>
+  </si>
+  <si>
+    <t>BAHAN MINUMAN</t>
+  </si>
+  <si>
+    <t>01.1.8.1.001</t>
+  </si>
+  <si>
+    <t>Gula pasir</t>
+  </si>
+  <si>
+    <t>01.1.8.1.002</t>
+  </si>
+  <si>
+    <t>Gula merah, gula air (pohom aren, kelapa, lontar)</t>
+  </si>
+  <si>
+    <t>01.2.1.2.001</t>
+  </si>
+  <si>
+    <t>Teh bubuk</t>
+  </si>
+  <si>
+    <t>01.2.1.2.002</t>
+  </si>
+  <si>
+    <t>Teh celup (sachet)</t>
+  </si>
+  <si>
+    <t>2 gr</t>
+  </si>
+  <si>
+    <t>2 g</t>
+  </si>
+  <si>
+    <t>1 tea bag sachet = 2 g</t>
+  </si>
+  <si>
+    <t>01.2.1.1.001</t>
+  </si>
+  <si>
+    <t>Kopi (bubuk, biji)</t>
+  </si>
+  <si>
+    <t>01.2.1.1.002</t>
+  </si>
+  <si>
+    <t>Kopi instan (sachet)</t>
+  </si>
+  <si>
+    <t>20 gr</t>
+  </si>
+  <si>
+    <t>20 g</t>
+  </si>
+  <si>
+    <t>1 instant coffee sachet = 20 g</t>
+  </si>
+  <si>
+    <t>01.2.2.2/3</t>
+  </si>
+  <si>
+    <t>Bahan minuman lainnya</t>
+  </si>
+  <si>
+    <t>Average from other items in the same category (items 126-131), 70.33 rounded to 70 g</t>
+  </si>
+  <si>
+    <t>BUMBU-BUMBUAN</t>
+  </si>
+  <si>
+    <t>01.1.9.2.001</t>
+  </si>
+  <si>
+    <t>Garam</t>
+  </si>
+  <si>
+    <t>unit is already in gram</t>
+  </si>
+  <si>
+    <t>01.1.9.2.005</t>
+  </si>
+  <si>
+    <t>Kemiri</t>
+  </si>
+  <si>
+    <t>01.1.9.2.006</t>
+  </si>
+  <si>
+    <t>Ketumbar/jinten</t>
+  </si>
+  <si>
+    <t>01.1.9.2.007</t>
+  </si>
+  <si>
+    <t>Merica/lada</t>
+  </si>
+  <si>
+    <t>01.1.7.3.024</t>
+  </si>
+  <si>
+    <t>Asam</t>
+  </si>
+  <si>
+    <t>01.1.9.4.003/4</t>
+  </si>
+  <si>
+    <t>Terasi/petis</t>
+  </si>
+  <si>
+    <t>01.1.9.1.003</t>
+  </si>
+  <si>
+    <t>Kecap</t>
+  </si>
+  <si>
+    <t>100 ml</t>
+  </si>
+  <si>
+    <t>unit is already in ml</t>
+  </si>
+  <si>
+    <t>01.1.9.4.008</t>
+  </si>
+  <si>
+    <t>Penyedap masakan/vetsin</t>
+  </si>
+  <si>
+    <t>01.1.9.1.005</t>
+  </si>
+  <si>
+    <t>Sambal jadi</t>
+  </si>
+  <si>
+    <t>01.1.9.1.006-7</t>
+  </si>
+  <si>
+    <t>Saus tomat</t>
+  </si>
+  <si>
+    <t>01.1.9.4.007</t>
+  </si>
+  <si>
+    <t>Bumbu masak jadi/kemasan, bumbu racikan</t>
+  </si>
+  <si>
+    <t>01.1.9.2.003/4</t>
+  </si>
+  <si>
+    <t>Bumbu dapur lainnya (pala, jahe, kunyit, dsb)</t>
+  </si>
+  <si>
+    <t>BAHAN MAKANAN LAINNYA</t>
+  </si>
+  <si>
+    <t>01.1.1.5.012</t>
+  </si>
+  <si>
+    <t>Mie instan</t>
+  </si>
+  <si>
+    <t>Bungkus (±80 gr)</t>
+  </si>
+  <si>
+    <t>Pack (±80 g)</t>
+  </si>
+  <si>
+    <t>1 pack of instant noodles = ±80 g</t>
+  </si>
+  <si>
+    <t>01.1.1.5.018/19</t>
+  </si>
+  <si>
+    <t>Kerupuk</t>
+  </si>
+  <si>
+    <t>01.1.1.5.013</t>
+  </si>
+  <si>
+    <t>Bubur bayi kemasan</t>
+  </si>
+  <si>
+    <t>Kotak kecil (±150 gr)</t>
+  </si>
+  <si>
+    <t>Small box (±150 g)</t>
+  </si>
+  <si>
+    <t>1 small box = ±150 g</t>
+  </si>
+  <si>
+    <t>01.1.1.2/15/76/94</t>
+  </si>
+  <si>
+    <t>Lainnya</t>
+  </si>
+  <si>
+    <t>Average from other items in the same category (items 147-149)</t>
+  </si>
+  <si>
+    <t>MAKANAN MINUMAN JADI</t>
+  </si>
+  <si>
+    <t>01.1.1.2.005</t>
+  </si>
+  <si>
+    <t>Roti tawar</t>
+  </si>
+  <si>
+    <t>Potong</t>
+  </si>
+  <si>
+    <t>Slice</t>
+  </si>
+  <si>
+    <t>1 slice of white bread = 60 g (6 slices = 360 g)</t>
+  </si>
+  <si>
+    <t>https://www.sarirotifoodsolutions.com/produk/info/roti-tawar-toast</t>
+  </si>
+  <si>
+    <t>01.1.1.2.003</t>
+  </si>
+  <si>
+    <t>Roti manis, roti lainnya</t>
+  </si>
+  <si>
+    <t>1 medium sweet bread roll ≈ 80 g</t>
+  </si>
+  <si>
+    <t>https://rottebakery.com/roti-tawar-atau-roti-manis-cek-kandungan-nutrisi/</t>
+  </si>
+  <si>
+    <t>11.1.1.1.025/044</t>
+  </si>
+  <si>
+    <t>Kue kering, biskuit, semprong</t>
+  </si>
+  <si>
+    <t>11.1.1.1.024/103/123</t>
+  </si>
+  <si>
+    <t>Kue basah (kue lapis, bika ambon, lemper, dsb)</t>
+  </si>
+  <si>
+    <t>Buah</t>
+  </si>
+  <si>
+    <t>ESTIMATE — 1 piece of kue basah ≈40–50 g (lemper/lapis are heavier); needs verification</t>
+  </si>
+  <si>
+    <t>11.1.1.1.133/83-89</t>
+  </si>
+  <si>
+    <t>Makanan gorengan</t>
+  </si>
+  <si>
+    <t>1 piece of fried snack (vegetable bakwan) ≈ 40–50 g</t>
+  </si>
+  <si>
+    <t>https://www.kompas.com/food/read/2025/04/11/112518275/kandungan-gizi-bakwan-sayur-goreng-berapa-kalori</t>
+  </si>
+  <si>
+    <t>11.1.1.1.011</t>
+  </si>
+  <si>
+    <t>Bubur kacang hijau</t>
+  </si>
+  <si>
+    <t>Porsi</t>
+  </si>
+  <si>
+    <t>Portion</t>
+  </si>
+  <si>
+    <t>1 portion = 50 gr</t>
+  </si>
+  <si>
+    <t>https://cookpad.com/id/resep/16183454?ref=search&amp;search_term=bubur+kacang+hijau</t>
+  </si>
+  <si>
+    <t>11.1.1.1.015</t>
+  </si>
+  <si>
+    <t>Gado-gado, ketoprak, pecel</t>
+  </si>
+  <si>
+    <t>1 portion of gado-gado ≈ 350–400 g</t>
+  </si>
+  <si>
+    <t>https://www.alodokter.com/kalori-gado-gado-dan-cara-sehat-menyantapnya</t>
+  </si>
+  <si>
+    <t>11.1.1.3.170</t>
+  </si>
+  <si>
+    <t>Nasi campur/rames</t>
+  </si>
+  <si>
+    <t>ESTIMATE — rice 100 g (1 scoop) plus side dishes; needs verification</t>
+  </si>
+  <si>
+    <t>11.1.1.3.169</t>
+  </si>
+  <si>
+    <t>Nasi goreng</t>
+  </si>
+  <si>
+    <t>1 standard portion of fried rice ≈ 200–250 g</t>
+  </si>
+  <si>
+    <t>https://www.halodoc.com/artikel/berapa-kalori-nasi-goreng-yang-aman-untuk-dikonsumsi</t>
+  </si>
+  <si>
+    <t>11.1.1.1.030</t>
+  </si>
+  <si>
+    <t>Nasi putih</t>
+  </si>
+  <si>
+    <t>1 portion = 1 scoop = 100 g cooked rice (DBMP/URT, Kemenkes)</t>
+  </si>
+  <si>
+    <t>https://www.studocu.id/id/document/universitas-muhammadiyah-jambi/social-health/daftar-bahan-makanan-penukar-dbmp/109250905</t>
+  </si>
+  <si>
+    <t>11.1.1.1.023</t>
+  </si>
+  <si>
+    <t>Lontong/ketupat sayur</t>
+  </si>
+  <si>
+    <t>ESTIMATE — 1 portion of lontong/ketupat sayur; needs verification</t>
+  </si>
+  <si>
+    <t>11.1.2.0.006/017/035/041/148</t>
+  </si>
+  <si>
+    <t>Soto, gule, sop, rawon, cincang</t>
+  </si>
+  <si>
+    <t>1 bowl of soto/gule/sop ≈ 350 g (broth ±350 ml plus solids)</t>
+  </si>
+  <si>
+    <t>https://ketikmedia.com/kesehatan/kalori-soto-ayam</t>
+  </si>
+  <si>
+    <t>11.1.1.1.178-180</t>
+  </si>
+  <si>
+    <t>Sayur matang (ditumis, disantan, dsb)</t>
+  </si>
+  <si>
+    <t>1 vegetable portion = 100 g (DBMP/URT; a vegetable portion is always 100 g)</t>
+  </si>
+  <si>
+    <t>https://ahligizi.id/blog/2019/11/21/ukuran-standar-porsi-bahan-makanan-food-exchange-list/</t>
+  </si>
+  <si>
+    <t>11.1.1.1.040</t>
+  </si>
+  <si>
+    <t>Sate, tongseng</t>
+  </si>
+  <si>
+    <t>Porsi/5 tusuk</t>
+  </si>
+  <si>
+    <t>Portion (5 skewers)</t>
+  </si>
+  <si>
+    <t>ESTIMATE — 1 portion = 5 satay skewers, ±14 g meat per skewer; needs verification</t>
+  </si>
+  <si>
+    <t>11.1.1.1.047</t>
+  </si>
+  <si>
+    <t>Mie bakso, mie rebus, mie goreng</t>
+  </si>
+  <si>
+    <t>1 portion of mie bakso/mie ayam = 240 g</t>
+  </si>
+  <si>
+    <t>https://hellosehat.com/nutrisi/fakta-gizi/kalori-mi-ayam/</t>
+  </si>
+  <si>
+    <t>11.1.1.1.029</t>
+  </si>
+  <si>
+    <t>ESTIMATE — 1 portion of cooked instant noodles (1 pack, 80 g dry, plus water); needs verification</t>
+  </si>
+  <si>
+    <t>11.1.1.1.027</t>
+  </si>
+  <si>
+    <t>Makanan ringan anak-anak, krupuk/kripik</t>
+  </si>
+  <si>
+    <t>11.1.1.1.019</t>
+  </si>
+  <si>
+    <t>Ikan matang</t>
+  </si>
+  <si>
+    <t>1 medium piece of fish = 40 g (DBMP/URT, Kemenkes)</t>
+  </si>
+  <si>
+    <t>11.1.1.1.007/8/11113034</t>
+  </si>
+  <si>
+    <t>Ayam/daging matang (ayam goreng, rendang, dsb)</t>
+  </si>
+  <si>
+    <t>1 medium piece of chicken/meat = 40 g (DBMP/URT, Kemenkes)</t>
+  </si>
+  <si>
+    <t>11.1.1.1.004/11111208</t>
+  </si>
+  <si>
+    <t>Daging olahan (sosis, nugget, daging asap, dsb) matang</t>
+  </si>
+  <si>
+    <t>ESTIMATE — 1 sausage ≈30–50 g, 1 nugget ≈15 g; needs verification</t>
+  </si>
+  <si>
+    <t>11.1.1.3.008</t>
+  </si>
+  <si>
+    <t>Bubur ayam</t>
+  </si>
+  <si>
+    <t>1 standard portion of chicken porridge ≈ 240–250 g</t>
+  </si>
+  <si>
+    <t>https://www.halodoc.com/artikel/ketahui-kalori-bubur-ayam-sebagai-menu-favorit-sarapan</t>
+  </si>
+  <si>
+    <t>11.1.1.3.003</t>
+  </si>
+  <si>
+    <t>Siomay, batagor</t>
+  </si>
+  <si>
+    <t>Porsi/5 potong</t>
+  </si>
+  <si>
+    <t>Portion (5 pieces)</t>
+  </si>
+  <si>
+    <t>ESTIMATE — 1 portion = 5 pieces of siomay, ±30 g per piece; needs verification</t>
+  </si>
+  <si>
+    <t>Makanan jadi lainnya</t>
+  </si>
+  <si>
+    <t>Average from other items in the same category (items 152-173)</t>
+  </si>
+  <si>
+    <t>11.1.1.1.058</t>
+  </si>
+  <si>
+    <t>Air kemasan</t>
+  </si>
+  <si>
     <t>liter</t>
   </si>
   <si>
     <t>1 liter</t>
   </si>
   <si>
-    <t>01.1.5.4.001/4</t>
-  </si>
-  <si>
-    <t>Minyak goreng (kelapa sawit, bunga matahari)</t>
-  </si>
-  <si>
-    <t>01.1.6.7.033</t>
-  </si>
-  <si>
-    <t>Kelapa (tidak termasuk santan instan)</t>
-  </si>
-  <si>
-    <t>ESTIMATE — grated coconut flesh from 1 medium coconut; needs verification</t>
-  </si>
-  <si>
-    <t>01.1.5.1/52/53/54</t>
-  </si>
-  <si>
-    <t>Minyak dan kelapa lainnya</t>
-  </si>
-  <si>
-    <t>Average from other items in the same category (items 121-123)</t>
-  </si>
-  <si>
-    <t>BAHAN MINUMAN</t>
-  </si>
-  <si>
-    <t>01.1.8.1.001</t>
-  </si>
-  <si>
-    <t>Gula pasir</t>
-  </si>
-  <si>
-    <t>01.1.8.1.002</t>
-  </si>
-  <si>
-    <t>Gula merah, gula air (pohom aren, kelapa, lontar)</t>
-  </si>
-  <si>
-    <t>01.2.1.2.001</t>
-  </si>
-  <si>
-    <t>Teh bubuk</t>
-  </si>
-  <si>
-    <t>01.2.1.2.002</t>
-  </si>
-  <si>
-    <t>Teh celup (sachet)</t>
-  </si>
-  <si>
-    <t>2 gr</t>
-  </si>
-  <si>
-    <t>2 g</t>
-  </si>
-  <si>
-    <t>1 tea bag sachet = 2 g</t>
-  </si>
-  <si>
-    <t>01.2.1.1.001</t>
-  </si>
-  <si>
-    <t>Kopi (bubuk, biji)</t>
-  </si>
-  <si>
-    <t>01.2.1.1.002</t>
-  </si>
-  <si>
-    <t>Kopi instan (sachet)</t>
-  </si>
-  <si>
-    <t>20 gr</t>
-  </si>
-  <si>
-    <t>20 g</t>
-  </si>
-  <si>
-    <t>1 instant coffee sachet = 20 g</t>
-  </si>
-  <si>
-    <t>01.2.2.2/3</t>
-  </si>
-  <si>
-    <t>Bahan minuman lainnya</t>
-  </si>
-  <si>
-    <t>Average from other items in the same category (items 126-131), 70.33 rounded to 70 g</t>
-  </si>
-  <si>
-    <t>BUMBU-BUMBUAN</t>
-  </si>
-  <si>
-    <t>01.1.9.2.001</t>
-  </si>
-  <si>
-    <t>Garam</t>
-  </si>
-  <si>
-    <t>Gram</t>
-  </si>
-  <si>
-    <t>unit is already in gram</t>
-  </si>
-  <si>
-    <t>01.1.9.2.005</t>
-  </si>
-  <si>
-    <t>Kemiri</t>
-  </si>
-  <si>
-    <t>01.1.9.2.006</t>
-  </si>
-  <si>
-    <t>Ketumbar/jinten</t>
-  </si>
-  <si>
-    <t>01.1.9.2.007</t>
-  </si>
-  <si>
-    <t>Merica/lada</t>
-  </si>
-  <si>
-    <t>01.1.7.3.024</t>
-  </si>
-  <si>
-    <t>Asam</t>
-  </si>
-  <si>
-    <t>01.1.9.4.003/4</t>
-  </si>
-  <si>
-    <t>Terasi/petis</t>
-  </si>
-  <si>
-    <t>01.1.9.1.003</t>
-  </si>
-  <si>
-    <t>Kecap</t>
-  </si>
-  <si>
-    <t>100 ml</t>
-  </si>
-  <si>
-    <t>unit is already in ml</t>
-  </si>
-  <si>
-    <t>01.1.9.4.008</t>
-  </si>
-  <si>
-    <t>Penyedap masakan/vetsin</t>
-  </si>
-  <si>
-    <t>01.1.9.1.005</t>
-  </si>
-  <si>
-    <t>Sambal jadi</t>
-  </si>
-  <si>
-    <t>01.1.9.1.006-7</t>
-  </si>
-  <si>
-    <t>Saus tomat</t>
-  </si>
-  <si>
-    <t>01.1.9.4.007</t>
-  </si>
-  <si>
-    <t>Bumbu maskan jadi/kemasan, bumbu racikan</t>
-  </si>
-  <si>
-    <t>01.1.9.2.003/4</t>
-  </si>
-  <si>
-    <t>Bumbu dapur lainnya (pala, jahe, kunyit, dsb)</t>
-  </si>
-  <si>
-    <t>BAHAN MAKANAN LAINNYA</t>
-  </si>
-  <si>
-    <t>01.1.1.5.012</t>
-  </si>
-  <si>
-    <t>Mie instan</t>
-  </si>
-  <si>
-    <t>Bungkus (±80 gr)</t>
-  </si>
-  <si>
-    <t>Pack (±80 g)</t>
-  </si>
-  <si>
-    <t>1 pack of instant noodles = ±80 g</t>
-  </si>
-  <si>
-    <t>01.1.1.5.018/19</t>
-  </si>
-  <si>
-    <t>Kerupuk</t>
-  </si>
-  <si>
-    <t>01.1.1.5.013</t>
-  </si>
-  <si>
-    <t>Bubur bayi kemasan</t>
-  </si>
-  <si>
-    <t>Kotak kecil (±150 gr)</t>
-  </si>
-  <si>
-    <t>Small box (±150 g)</t>
-  </si>
-  <si>
-    <t>1 small box = ±150 g</t>
-  </si>
-  <si>
-    <t>01.1.1.2/15/76/94</t>
-  </si>
-  <si>
-    <t>Lainnya</t>
-  </si>
-  <si>
-    <t>Average from other items in the same category (items 147-149)</t>
-  </si>
-  <si>
-    <t>MAKANAN MINUMAN JADI</t>
-  </si>
-  <si>
-    <t>01.1.1.2.005</t>
-  </si>
-  <si>
-    <t>Roti tawar</t>
-  </si>
-  <si>
-    <t>Potong</t>
-  </si>
-  <si>
-    <t>Slice</t>
-  </si>
-  <si>
-    <t>1 slice of white bread = 60 g (6 slices = 360 g)</t>
-  </si>
-  <si>
-    <t>https://www.sarirotifoodsolutions.com/produk/info/roti-tawar-toast</t>
-  </si>
-  <si>
-    <t>01.1.1.2.003</t>
-  </si>
-  <si>
-    <t>Roti manis, roti lainnya</t>
-  </si>
-  <si>
-    <t>1 medium sweet bread roll ≈ 80 g</t>
-  </si>
-  <si>
-    <t>https://rottebakery.com/roti-tawar-atau-roti-manis-cek-kandungan-nutrisi/</t>
-  </si>
-  <si>
-    <t>11.1.1.1.025/044</t>
-  </si>
-  <si>
-    <t>Kue kering, biskuit, semprong</t>
-  </si>
-  <si>
-    <t>11.1.1.1.024/103/123</t>
-  </si>
-  <si>
-    <t>Kue basah (kue lapis, bika ambon, lemper, dsb)</t>
-  </si>
-  <si>
-    <t>Buah</t>
-  </si>
-  <si>
-    <t>ESTIMATE — 1 piece of kue basah ≈40–50 g (lemper/lapis are heavier); needs verification</t>
-  </si>
-  <si>
-    <t>11.1.1.1.133/83-89</t>
-  </si>
-  <si>
-    <t>Makanan gorengan</t>
-  </si>
-  <si>
-    <t>1 piece of fried snack (vegetable bakwan) ≈ 40–50 g</t>
-  </si>
-  <si>
-    <t>https://www.kompas.com/food/read/2025/04/11/112518275/kandungan-gizi-bakwan-sayur-goreng-berapa-kalori</t>
-  </si>
-  <si>
-    <t>11.1.1.1.011</t>
-  </si>
-  <si>
-    <t>Bubur kacang hijau</t>
-  </si>
-  <si>
-    <t>Porsi</t>
-  </si>
-  <si>
-    <t>Portion</t>
-  </si>
-  <si>
-    <t>1 portion = 50 gr</t>
-  </si>
-  <si>
-    <t>https://cookpad.com/id/resep/16183454?ref=search&amp;search_term=bubur+kacang+hijau</t>
-  </si>
-  <si>
-    <t>11.1.1.1.015</t>
-  </si>
-  <si>
-    <t>Gado-gado, ketoprak, pecel</t>
-  </si>
-  <si>
-    <t>1 portion of gado-gado ≈ 350–400 g</t>
-  </si>
-  <si>
-    <t>https://www.alodokter.com/kalori-gado-gado-dan-cara-sehat-menyantapnya</t>
-  </si>
-  <si>
-    <t>11.1.1.3.170</t>
-  </si>
-  <si>
-    <t>Nasi campur/rames</t>
-  </si>
-  <si>
-    <t>ESTIMATE — rice 100 g (1 scoop) plus side dishes; needs verification</t>
-  </si>
-  <si>
-    <t>11.1.1.3.169</t>
-  </si>
-  <si>
-    <t>Nasi goreng</t>
-  </si>
-  <si>
-    <t>1 standard portion of fried rice ≈ 200–250 g</t>
-  </si>
-  <si>
-    <t>https://www.halodoc.com/artikel/berapa-kalori-nasi-goreng-yang-aman-untuk-dikonsumsi</t>
-  </si>
-  <si>
-    <t>11.1.1.1.030</t>
-  </si>
-  <si>
-    <t>Nasi putih</t>
-  </si>
-  <si>
-    <t>1 portion = 1 scoop = 100 g cooked rice (DBMP/URT, Kemenkes)</t>
-  </si>
-  <si>
-    <t>https://www.studocu.id/id/document/universitas-muhammadiyah-jambi/social-health/daftar-bahan-makanan-penukar-dbmp/109250905</t>
-  </si>
-  <si>
-    <t>11.1.1.1.023</t>
-  </si>
-  <si>
-    <t>Lontong/ketupat sayur</t>
-  </si>
-  <si>
-    <t>ESTIMATE — 1 portion of lontong/ketupat sayur; needs verification</t>
-  </si>
-  <si>
-    <t>11.1.2.0.006/017/035/041/148</t>
-  </si>
-  <si>
-    <t>Soto, gule, sop, rawon, cincang</t>
-  </si>
-  <si>
-    <t>1 bowl of soto/gule/sop ≈ 350 g (broth ±350 ml plus solids)</t>
-  </si>
-  <si>
-    <t>https://ketikmedia.com/kesehatan/kalori-soto-ayam</t>
-  </si>
-  <si>
-    <t>11.1.1.1.178-180</t>
-  </si>
-  <si>
-    <t>Sayur matang (ditumis, disantan, dsb)</t>
-  </si>
-  <si>
-    <t>1 vegetable portion = 100 g (DBMP/URT; a vegetable portion is always 100 g)</t>
-  </si>
-  <si>
-    <t>https://ahligizi.id/blog/2019/11/21/ukuran-standar-porsi-bahan-makanan-food-exchange-list/</t>
-  </si>
-  <si>
-    <t>11.1.1.1.040</t>
-  </si>
-  <si>
-    <t>Sate, tongseng</t>
-  </si>
-  <si>
-    <t>Porsi/5 tusuk</t>
-  </si>
-  <si>
-    <t>Portion (5 skewers)</t>
-  </si>
-  <si>
-    <t>ESTIMATE — 1 portion = 5 satay skewers, ±14 g meat per skewer; needs verification</t>
-  </si>
-  <si>
-    <t>11.1.1.1.047</t>
-  </si>
-  <si>
-    <t>Mie bakso, mie rebus, mie goreng</t>
-  </si>
-  <si>
-    <t>1 portion of mie bakso/mie ayam = 240 g</t>
-  </si>
-  <si>
-    <t>https://hellosehat.com/nutrisi/fakta-gizi/kalori-mi-ayam/</t>
-  </si>
-  <si>
-    <t>11.1.1.1.029</t>
-  </si>
-  <si>
-    <t>ESTIMATE — 1 portion of cooked instant noodles (1 pack, 80 g dry, plus water); needs verification</t>
-  </si>
-  <si>
-    <t>11.1.1.1.027</t>
-  </si>
-  <si>
-    <t>Makanan ringan anak-anak, krupuk/kripik</t>
-  </si>
-  <si>
-    <t>11.1.1.1.019</t>
-  </si>
-  <si>
-    <t>Ikan matang</t>
-  </si>
-  <si>
-    <t>1 medium piece of fish = 40 g (DBMP/URT, Kemenkes)</t>
-  </si>
-  <si>
-    <t>11.1.1.1.007/8/11113034</t>
-  </si>
-  <si>
-    <t>Ayam/daging matang (ayam goreng, rendang, dsb)</t>
-  </si>
-  <si>
-    <t>1 medium piece of chicken/meat = 40 g (DBMP/URT, Kemenkes)</t>
-  </si>
-  <si>
-    <t>11.1.1.1.004/11111208</t>
-  </si>
-  <si>
-    <t>Daging olahan (sosis, nugget, daging asap, dsb) matang</t>
-  </si>
-  <si>
-    <t>ESTIMATE — 1 sausage ≈30–50 g, 1 nugget ≈15 g; needs verification</t>
-  </si>
-  <si>
-    <t>11.1.1.3.008</t>
-  </si>
-  <si>
-    <t>Bubur ayam</t>
-  </si>
-  <si>
-    <t>1 standard portion of chicken porridge ≈ 240–250 g</t>
-  </si>
-  <si>
-    <t>https://www.halodoc.com/artikel/ketahui-kalori-bubur-ayam-sebagai-menu-favorit-sarapan</t>
-  </si>
-  <si>
-    <t>11.1.1.3.003</t>
-  </si>
-  <si>
-    <t>Siomay, batagor</t>
-  </si>
-  <si>
-    <t>Porsi/5 potong</t>
-  </si>
-  <si>
-    <t>Portion (5 pieces)</t>
-  </si>
-  <si>
-    <t>ESTIMATE — 1 portion = 5 pieces of siomay, ±30 g per piece; needs verification</t>
-  </si>
-  <si>
-    <t>Makanan jadi lainnya</t>
-  </si>
-  <si>
-    <t>Average from other items in the same category (items 152-173)</t>
-  </si>
-  <si>
-    <t>11.1.1.1.058</t>
-  </si>
-  <si>
-    <t>Air kemasan</t>
-  </si>
-  <si>
     <t>01.2.2.1.000</t>
   </si>
   <si>
@@ -1467,6 +1457,9 @@
   </si>
   <si>
     <t>Rokok dan tembakau Lainnya</t>
+  </si>
+  <si>
+    <t>ESTIMATE — grated coconut flesh from 1 medium coconut</t>
   </si>
 </sst>
 </file>
@@ -1938,8 +1931,8 @@
     <col min="7" max="7" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="102" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="113.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.83203125" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="10.83203125" style="2"/>
+    <col min="10" max="12" width="10.83203125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3907,10 +3900,10 @@
         <v>166</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F72" s="10">
         <v>342.5</v>
@@ -3919,10 +3912,10 @@
         <v>136</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
@@ -3930,18 +3923,18 @@
         <v>72</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B74" s="1">
         <v>73</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>12</v>
@@ -3964,13 +3957,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B75" s="1">
         <v>74</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>12</v>
@@ -3993,13 +3986,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B76" s="1">
         <v>75</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>12</v>
@@ -4022,13 +4015,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B77" s="1">
         <v>76</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>12</v>
@@ -4051,13 +4044,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B78" s="1">
         <v>77</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>12</v>
@@ -4080,13 +4073,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B79" s="1">
         <v>78</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>12</v>
@@ -4109,13 +4102,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B80" s="1">
         <v>79</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>12</v>
@@ -4138,13 +4131,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B81" s="1">
         <v>80</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>12</v>
@@ -4167,13 +4160,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B82" s="1">
         <v>81</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>12</v>
@@ -4196,13 +4189,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B83" s="1">
         <v>82</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>12</v>
@@ -4225,13 +4218,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B84" s="1">
         <v>83</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>12</v>
@@ -4254,13 +4247,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B85" s="1">
         <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>12</v>
@@ -4283,13 +4276,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B86" s="1">
         <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>12</v>
@@ -4312,13 +4305,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B87" s="1">
         <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>12</v>
@@ -4341,19 +4334,19 @@
     </row>
     <row r="88" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B88" s="1">
         <v>87</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F88" s="9">
         <v>250</v>
@@ -4362,24 +4355,24 @@
         <v>136</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B89" s="1">
         <v>88</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F89" s="9">
         <v>200</v>
@@ -4388,18 +4381,18 @@
         <v>136</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B90" s="1">
         <v>89</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>12</v>
@@ -4422,13 +4415,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B91" s="1">
         <v>90</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>12</v>
@@ -4451,13 +4444,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B92" s="1">
         <v>91</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>12</v>
@@ -4480,13 +4473,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B93" s="1">
         <v>92</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>86</v>
@@ -4498,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>88</v>
@@ -4509,13 +4502,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B94" s="1">
         <v>93</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>86</v>
@@ -4527,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>88</v>
@@ -4538,13 +4531,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B95" s="1">
         <v>94</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
@@ -4567,13 +4560,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B96" s="1">
         <v>95</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>12</v>
@@ -4596,13 +4589,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B97" s="1">
         <v>96</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>12</v>
@@ -4625,13 +4618,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B98" s="1">
         <v>97</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
@@ -4657,18 +4650,18 @@
         <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B100" s="1">
         <v>99</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>12</v>
@@ -4691,13 +4684,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B101" s="1">
         <v>100</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
@@ -4720,13 +4713,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B102" s="1">
         <v>101</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>12</v>
@@ -4749,13 +4742,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B103" s="1">
         <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>12</v>
@@ -4778,13 +4771,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B104" s="1">
         <v>103</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>12</v>
@@ -4807,13 +4800,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B105" s="1">
         <v>104</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>86</v>
@@ -4825,7 +4818,7 @@
         <v>1</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>88</v>
@@ -4836,13 +4829,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B106" s="1">
         <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>86</v>
@@ -4854,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>88</v>
@@ -4868,18 +4861,18 @@
         <v>106</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B108" s="1">
         <v>107</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>12</v>
@@ -4902,13 +4895,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B109" s="1">
         <v>108</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>12</v>
@@ -4931,13 +4924,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B110" s="1">
         <v>109</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>12</v>
@@ -4960,13 +4953,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B111" s="1">
         <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>12</v>
@@ -4989,13 +4982,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B112" s="1">
         <v>111</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>12</v>
@@ -5018,13 +5011,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B113" s="1">
         <v>112</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>12</v>
@@ -5047,13 +5040,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B114" s="1">
         <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>12</v>
@@ -5076,13 +5069,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B115" s="1">
         <v>114</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>12</v>
@@ -5105,13 +5098,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B116" s="1">
         <v>115</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>12</v>
@@ -5134,13 +5127,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B117" s="1">
         <v>116</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>12</v>
@@ -5163,13 +5156,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B118" s="1">
         <v>117</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>12</v>
@@ -5192,13 +5185,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B119" s="1">
         <v>118</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
@@ -5224,7 +5217,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>12</v>
@@ -5250,30 +5243,30 @@
         <v>120</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B122" s="1">
         <v>121</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F122" s="9">
-        <v>1</v>
+        <v>920</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>271</v>
@@ -5293,19 +5286,19 @@
         <v>273</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F123" s="9">
-        <v>1</v>
+        <v>920</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>14</v>
@@ -5313,13 +5306,13 @@
     </row>
     <row r="124" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1">
         <v>123</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>134</v>
@@ -5334,7 +5327,7 @@
         <v>136</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>276</v>
+        <v>479</v>
       </c>
     </row>
     <row r="125" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -5348,13 +5341,13 @@
         <v>278</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F125" s="10">
-        <v>800</v>
+        <v>746.67</v>
       </c>
       <c r="G125" s="13" t="s">
         <v>136</v>
@@ -5363,7 +5356,7 @@
         <v>279</v>
       </c>
       <c r="I125" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
@@ -5394,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>88</v>
@@ -5423,7 +5416,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>88</v>
@@ -5452,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>88</v>
@@ -5510,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>88</v>
@@ -5559,10 +5552,10 @@
         <v>300</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F133" s="10">
         <v>70</v>
@@ -5574,7 +5567,7 @@
         <v>301</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
@@ -5596,10 +5589,10 @@
         <v>304</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F135" s="9">
         <v>1</v>
@@ -5608,7 +5601,7 @@
         <v>136</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>14</v>
@@ -5616,19 +5609,19 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B136" s="1">
         <v>135</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F136" s="9">
         <v>1</v>
@@ -5637,7 +5630,7 @@
         <v>136</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>14</v>
@@ -5645,19 +5638,19 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B137" s="1">
         <v>136</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F137" s="9">
         <v>1</v>
@@ -5666,7 +5659,7 @@
         <v>136</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>14</v>
@@ -5674,19 +5667,19 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B138" s="1">
         <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F138" s="9">
         <v>1</v>
@@ -5695,7 +5688,7 @@
         <v>136</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>14</v>
@@ -5703,19 +5696,19 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B139" s="1">
         <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F139" s="9">
         <v>1</v>
@@ -5724,7 +5717,7 @@
         <v>136</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>14</v>
@@ -5732,19 +5725,19 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B140" s="1">
         <v>139</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F140" s="9">
         <v>1</v>
@@ -5753,7 +5746,7 @@
         <v>136</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>14</v>
@@ -5761,19 +5754,19 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B141" s="1">
         <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D141" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="E141" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F141" s="9">
         <v>100</v>
@@ -5782,7 +5775,7 @@
         <v>154</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>14</v>
@@ -5790,19 +5783,19 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B142" s="1">
         <v>141</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F142" s="9">
         <v>1</v>
@@ -5811,7 +5804,7 @@
         <v>136</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>14</v>
@@ -5819,19 +5812,19 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B143" s="1">
         <v>142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F143" s="9">
         <v>100</v>
@@ -5840,7 +5833,7 @@
         <v>154</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>14</v>
@@ -5848,19 +5841,19 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B144" s="1">
         <v>143</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F144" s="9">
         <v>100</v>
@@ -5869,7 +5862,7 @@
         <v>154</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>14</v>
@@ -5877,19 +5870,19 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B145" s="1">
         <v>144</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F145" s="9">
         <v>1</v>
@@ -5898,7 +5891,7 @@
         <v>136</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>14</v>
@@ -5906,19 +5899,19 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B146" s="1">
         <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F146" s="9">
         <v>1</v>
@@ -5927,7 +5920,7 @@
         <v>136</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>14</v>
@@ -5938,24 +5931,24 @@
         <v>146</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B148" s="1">
         <v>147</v>
       </c>
       <c r="C148" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D148" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="E148" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="F148" s="9">
         <v>80</v>
@@ -5964,7 +5957,7 @@
         <v>136</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>14</v>
@@ -5972,13 +5965,13 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B149" s="1">
         <v>148</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>86</v>
@@ -5990,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>88</v>
@@ -6001,19 +5994,19 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B150" s="1">
         <v>149</v>
       </c>
       <c r="C150" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D150" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="E150" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="F150" s="9">
         <v>150</v>
@@ -6022,7 +6015,7 @@
         <v>136</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I150" s="2" t="s">
         <v>14</v>
@@ -6030,19 +6023,19 @@
     </row>
     <row r="151" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A151" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B151" s="6">
         <v>150</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F151" s="10">
         <v>110</v>
@@ -6051,10 +6044,10 @@
         <v>136</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I151" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
@@ -6062,24 +6055,24 @@
         <v>151</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B153" s="1">
         <v>152</v>
       </c>
       <c r="C153" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="E153" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="F153" s="9">
         <v>60</v>
@@ -6088,27 +6081,27 @@
         <v>136</v>
       </c>
       <c r="H153" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="I153" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B154" s="2">
         <v>153</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D154" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="F154" s="9">
         <v>80</v>
@@ -6117,21 +6110,21 @@
         <v>136</v>
       </c>
       <c r="H154" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I154" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="I154" s="2" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B155" s="1">
         <v>154</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>86</v>
@@ -6143,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>88</v>
@@ -6154,16 +6147,16 @@
     </row>
     <row r="156" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B156" s="1">
         <v>155</v>
       </c>
       <c r="C156" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D156" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>135</v>
@@ -6175,21 +6168,21 @@
         <v>136</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B157" s="1">
         <v>156</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>135</v>
@@ -6201,27 +6194,27 @@
         <v>136</v>
       </c>
       <c r="H157" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I157" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="I157" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B158" s="2">
         <v>157</v>
       </c>
       <c r="C158" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D158" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="E158" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F158" s="9">
         <v>50</v>
@@ -6230,27 +6223,27 @@
         <v>136</v>
       </c>
       <c r="H158" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="I158" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="I158" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B159" s="1">
         <v>158</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D159" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F159" s="9">
         <v>400</v>
@@ -6259,27 +6252,27 @@
         <v>136</v>
       </c>
       <c r="H159" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I159" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="I159" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B160" s="1">
         <v>159</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D160" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F160" s="9">
         <v>300</v>
@@ -6288,24 +6281,24 @@
         <v>136</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B161" s="1">
         <v>160</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D161" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F161" s="9">
         <v>250</v>
@@ -6314,27 +6307,27 @@
         <v>136</v>
       </c>
       <c r="H161" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I161" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="I161" s="2" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B162" s="1">
         <v>161</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D162" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E162" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F162" s="9">
         <v>100</v>
@@ -6343,27 +6336,27 @@
         <v>136</v>
       </c>
       <c r="H162" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I162" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="I162" s="2" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B163" s="1">
         <v>162</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D163" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F163" s="9">
         <v>300</v>
@@ -6372,24 +6365,24 @@
         <v>136</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B164" s="1">
         <v>163</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D164" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E164" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F164" s="9">
         <v>350</v>
@@ -6398,27 +6391,27 @@
         <v>136</v>
       </c>
       <c r="H164" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="I164" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="I164" s="2" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B165" s="1">
         <v>164</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D165" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F165" s="9">
         <v>100</v>
@@ -6427,27 +6420,27 @@
         <v>136</v>
       </c>
       <c r="H165" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="I165" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="I165" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B166" s="1">
         <v>165</v>
       </c>
       <c r="C166" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D166" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="E166" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="F166" s="9">
         <v>70</v>
@@ -6456,24 +6449,24 @@
         <v>136</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B167" s="1">
         <v>166</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D167" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F167" s="9">
         <v>240</v>
@@ -6482,27 +6475,27 @@
         <v>136</v>
       </c>
       <c r="H167" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="I167" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="I167" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B168" s="1">
         <v>167</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D168" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E168" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F168" s="9">
         <v>200</v>
@@ -6511,18 +6504,18 @@
         <v>136</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B169" s="1">
         <v>168</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>86</v>
@@ -6534,7 +6527,7 @@
         <v>1</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>88</v>
@@ -6545,16 +6538,16 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B170" s="1">
         <v>169</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>135</v>
@@ -6566,24 +6559,24 @@
         <v>136</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B171" s="1">
         <v>170</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>135</v>
@@ -6595,24 +6588,24 @@
         <v>136</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B172" s="1">
         <v>171</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>135</v>
@@ -6624,24 +6617,24 @@
         <v>136</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B173" s="1">
         <v>172</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D173" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F173" s="9">
         <v>240</v>
@@ -6650,27 +6643,27 @@
         <v>136</v>
       </c>
       <c r="H173" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I173" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="I173" s="2" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B174" s="1">
         <v>173</v>
       </c>
       <c r="C174" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D174" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="E174" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="F174" s="9">
         <v>150</v>
@@ -6679,7 +6672,7 @@
         <v>136</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.15">
@@ -6687,13 +6680,13 @@
         <v>174</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="E175" s="13" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="F175" s="10">
         <v>150</v>
@@ -6702,36 +6695,36 @@
         <v>136</v>
       </c>
       <c r="H175" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I175" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B176" s="1">
         <v>175</v>
       </c>
       <c r="C176" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F176" s="9">
+        <v>1</v>
+      </c>
+      <c r="G176" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D176" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F176" s="9">
-        <v>1</v>
-      </c>
-      <c r="G176" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="H176" s="2" t="s">
-        <v>271</v>
+        <v>435</v>
       </c>
       <c r="I176" s="2" t="s">
         <v>14</v>
@@ -6739,28 +6732,28 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B177" s="1">
         <v>176</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F177" s="9">
         <v>1</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I177" s="2" t="s">
         <v>14</v>
@@ -6768,19 +6761,19 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B178" s="1">
         <v>177</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F178" s="9">
         <v>250</v>
@@ -6789,7 +6782,7 @@
         <v>154</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I178" s="2" t="s">
         <v>14</v>
@@ -6797,19 +6790,19 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B179" s="1">
         <v>178</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F179" s="9">
         <v>200</v>
@@ -6818,7 +6811,7 @@
         <v>154</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I179" s="2" t="s">
         <v>14</v>
@@ -6826,19 +6819,19 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B180" s="1">
         <v>179</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F180" s="9">
         <v>240</v>
@@ -6847,27 +6840,27 @@
         <v>154</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B181" s="1">
         <v>180</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F181" s="9">
         <v>60</v>
@@ -6876,24 +6869,24 @@
         <v>136</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B182" s="1">
         <v>181</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D182" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E182" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F182" s="9">
         <v>200</v>
@@ -6902,33 +6895,33 @@
         <v>136</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B183" s="1">
         <v>182</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F183" s="9">
         <v>1</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>270</v>
+        <v>434</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>271</v>
+        <v>435</v>
       </c>
       <c r="I183" s="2" t="s">
         <v>14</v>
@@ -6939,33 +6932,33 @@
         <v>183</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B185" s="1">
         <v>184</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F185" s="9">
         <v>1</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I185" s="2" t="s">
         <v>14</v>
@@ -6973,28 +6966,28 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B186" s="1">
         <v>185</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F186" s="9">
         <v>1</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I186" s="2" t="s">
         <v>14</v>
@@ -7002,28 +6995,28 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B187" s="1">
         <v>186</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F187" s="9">
         <v>1</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I187" s="2" t="s">
         <v>14</v>
@@ -7031,13 +7024,13 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B188" s="1">
         <v>187</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>86</v>
@@ -7049,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>88</v>
@@ -7063,7 +7056,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
